--- a/docs/400G_SR4_OSFP软硬件接口文档.xlsx
+++ b/docs/400G_SR4_OSFP软硬件接口文档.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ym_ti\Desktop\400G_SR4_OSFP_beta\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86177\Desktop\project\400G_SR4_OSFP\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBC956C-E7B7-4352-9B38-5CFAB434200A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898F8CEE-567F-4C16-A96F-AB0EA8D5CF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CHIP" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="ADC" sheetId="5" r:id="rId5"/>
     <sheet name="DAC" sheetId="7" r:id="rId6"/>
     <sheet name="POWERUP" sheetId="8" r:id="rId7"/>
+    <sheet name="FLASH" sheetId="10" r:id="rId8"/>
+    <sheet name="SRAM" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="192">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -780,7 +782,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用于任务调度器</t>
+    <t>用于任务调度器:TASK_ID_BASE_AD_SAMPLES:delay 100ms interval 400ms infinity exe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TASK_ID_RSSI_AD_SAMPLES:delay 100ms interval 00ms infinity exe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -831,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -842,6 +848,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1383,13 +1395,13 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" t="s">
         <v>44</v>
@@ -1419,13 +1431,13 @@
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -1440,11 +1452,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="4"/>
       <c r="E5" t="s">
         <v>53</v>
@@ -1453,13 +1465,13 @@
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1474,33 +1486,33 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1545,6 +1557,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="F6:F9"/>
@@ -1556,16 +1578,6 @@
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1620,7 +1632,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>130</v>
       </c>
       <c r="C2" t="s">
@@ -1649,7 +1661,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="5"/>
       <c r="C3" t="s">
         <v>74</v>
       </c>
@@ -1673,7 +1685,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="5"/>
       <c r="C4" t="s">
         <v>80</v>
       </c>
@@ -1697,7 +1709,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="5"/>
       <c r="C5" t="s">
         <v>84</v>
       </c>
@@ -1721,7 +1733,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
       <c r="C6" t="s">
         <v>87</v>
       </c>
@@ -1745,7 +1757,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="5"/>
       <c r="C7" t="s">
         <v>90</v>
       </c>
@@ -1769,7 +1781,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="5"/>
       <c r="C8" t="s">
         <v>93</v>
       </c>
@@ -1790,7 +1802,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="5"/>
       <c r="C9" t="s">
         <v>96</v>
       </c>
@@ -1814,7 +1826,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="5"/>
       <c r="C10" t="s">
         <v>105</v>
       </c>
@@ -1838,7 +1850,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="5"/>
       <c r="C11" t="s">
         <v>108</v>
       </c>
@@ -1862,7 +1874,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>111</v>
       </c>
@@ -1886,7 +1898,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="5"/>
       <c r="C13" t="s">
         <v>115</v>
       </c>
@@ -1907,7 +1919,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="5"/>
       <c r="C14" t="s">
         <v>114</v>
       </c>
@@ -1928,7 +1940,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="5"/>
       <c r="C15" t="s">
         <v>170</v>
       </c>
@@ -1952,7 +1964,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="5"/>
       <c r="C16" t="s">
         <v>122</v>
       </c>
@@ -1976,7 +1988,7 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="5"/>
       <c r="C17" t="s">
         <v>125</v>
       </c>
@@ -2000,7 +2012,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="5"/>
       <c r="C18" t="s">
         <v>128</v>
       </c>
@@ -2028,13 +2040,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8BB438-4D47-4773-BD17-3E53C37DD0AA}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="5" width="13.88671875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
-    <col min="7" max="7" width="26.109375" customWidth="1"/>
+    <col min="7" max="7" width="43.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2079,37 +2091,56 @@
       <c r="E2" t="s">
         <v>186</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>0</v>
       </c>
       <c r="G2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="6" t="s">
         <v>190</v>
       </c>
     </row>
+    <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2165,7 +2196,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>130</v>
       </c>
       <c r="C2" t="s">
@@ -2191,7 +2222,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="5"/>
       <c r="C3" t="s">
         <v>138</v>
       </c>
@@ -2215,7 +2246,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="5"/>
       <c r="C4" t="s">
         <v>145</v>
       </c>
@@ -2239,7 +2270,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="5"/>
       <c r="C5" t="s">
         <v>146</v>
       </c>
@@ -2263,7 +2294,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
       <c r="C6" t="s">
         <v>151</v>
       </c>
@@ -2287,7 +2318,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="5"/>
       <c r="C7" t="s">
         <v>152</v>
       </c>
@@ -2311,7 +2342,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="5"/>
       <c r="C8" t="s">
         <v>153</v>
       </c>
@@ -2335,7 +2366,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="5"/>
       <c r="C9" t="s">
         <v>154</v>
       </c>
@@ -2359,7 +2390,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="5"/>
       <c r="C10" t="s">
         <v>155</v>
       </c>
@@ -2383,7 +2414,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="5"/>
       <c r="C11" t="s">
         <v>156</v>
       </c>
@@ -2459,46 +2490,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+      <c r="B13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
+      <c r="B15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2517,4 +2548,24 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9173D5-BCC6-4527-872D-DCF064DCB0AB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30571DD-1797-495A-8461-5FA211236C07}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>